--- a/FILES/VENTE_PAR_CATEGORIE/category-sales-summary-2026-10-04-2026-10-04.xlsx
+++ b/FILES/VENTE_PAR_CATEGORIE/category-sales-summary-2026-10-04-2026-10-04.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FANOMEZANA\SUIVI SERVICE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FANOMEZANA\PROJETS\NOUVEAUX_RECAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79452BA8-FBA7-435F-8AF9-D0CAC019CBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC67BE07-DD70-4B8B-8A92-8CFB13ABA176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{B2C78A55-753A-4DBF-8C87-033E4898BD58}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{3480444E-5548-4BC0-B1D6-B34DAE3EB3B6}"/>
   </bookViews>
   <sheets>
     <sheet name="category-sales-summary-2026-10-" sheetId="1" r:id="rId1"/>
@@ -964,7 +964,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31127B80-71D2-409A-A2BB-779B37E1441B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA574E9-DD89-432D-B092-050889FF965C}">
   <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
